--- a/Notes and data for listed articles/(row 2) data for 2023 Ding et al./Long_format_Ab_protein_deposition.xlsx
+++ b/Notes and data for listed articles/(row 2) data for 2023 Ding et al./Long_format_Ab_protein_deposition.xlsx
@@ -52,7 +52,7 @@
     <t>WildType</t>
   </si>
   <si>
-    <t>hip</t>
+    <t>DG</t>
   </si>
   <si>
     <t>5xFAD</t>
